--- a/document/ppt/評審意見修正情形.xlsx
+++ b/document/ppt/評審意見修正情形.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\main\document\ppt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1AAD42-CEB3-40A1-9FD7-DEFA15692682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C27F73-A7D9-44DA-AEF2-BA38FEC5A93F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="評審" sheetId="1" r:id="rId1"/>
+    <sheet name="指導老師" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,11 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="32">
-  <si>
-    <t>評審委員_初評建議</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="48">
   <si>
     <t>完成日</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -53,9 +50,6 @@
     <t>YOLO訓練資料來源的介紹</t>
   </si>
   <si>
-    <t>皮膚病辨識</t>
-  </si>
-  <si>
     <t>增加AI醫療照護建議</t>
   </si>
   <si>
@@ -84,10 +78,6 @@
   </si>
   <si>
     <t>受傷追蹤，用動畫方式呈現傷口癒合狀態</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>增加傷口自我護埋知識的推薦</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -100,87 +90,139 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">由用戶所提供的
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>西元年(計算年齡)、疾病、個人習慣</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t>用戶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>傷口診斷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>模型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>預計規劃製作家庭群組功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>影像預處理、增加訓練資料數量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>藉由訓練資料的分級處理，讓模型進行分級訓練</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI提供護理建議的時候會依醫院的官網為標準</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增刺傷、手術型傷口–2種傷口類型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>針對受傷程度是否辨識的出來</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>建議是否需送醫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依據營業狀態變更圖標顏色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根據收藏狀態變更圖標樣式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加醫院收藏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指導老師建議-原系統_修正</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>建議內容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>評審委員_初評建議-原系統_修正</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>評審委員_初評建議-新功能開發</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>即時顯示附近醫院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>擴增傷口種類</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>將文字的護理步驟轉換成動畫呈現</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加入『傷口追蹤』、『傷口群組』功能，
+有分群的紀錄照片會以幻燈片的形式呈現</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>點擊『星星』按鈕後，地圖上的icon轉換成『星星』。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>附近醫院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升模型準確度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前最新模型的準確度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在使用者點擊『附近醫院』後，依使用者的位置，顯示距離他最近的10間醫療診所。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>透過Google Map API取得醫療診所的營業狀態，並給予對應狀態的icon顏色。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在醫療診所的小卡加上『星星』按鈕，點擊可以收藏/取消收藏，被收藏的會顯示在收藏表中，清楚表示。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增新增刺傷、手術型傷口–2種傷口類型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>原本規劃由AI生成護理動畫，但因品質不佳。
+修正為以固定圖片呈現，以確保專業正確性並符合資源限制。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>開始日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>由用戶所提供的
+西元年(計算年齡)、疾病、個人習慣
 作為AI判斷癒合時間、護理建議的標準</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用戶</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>傷口診斷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>模型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>原系統_修正</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>預計規劃製作家庭群組功能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>加入『傷口群組』功能，
-有分群的紀錄照片會以幻燈片的形式呈現</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新功能開發</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>影像預處理、增加訓練資料數量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>藉由訓練資料的分級處理，讓模型進行分級訓練</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AI提供護理建議的時候會依醫院的官網為標準</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新增刺傷、手術型傷口–2種傷口類型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>針對受傷程度是否辨識的出來</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>建議是否需送醫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>常見傷口管家</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -224,19 +266,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <family val="1"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0" tint="-0.34998626667073579"/>
       <name val="新細明體"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -266,7 +308,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -284,9 +326,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -302,20 +341,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -597,238 +669,453 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="65.625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="57.875" style="5" customWidth="1"/>
     <col min="3" max="3" width="53" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="9" style="1"/>
+    <col min="5" max="5" width="9" style="1"/>
+    <col min="6" max="6" width="10.25" style="19" customWidth="1"/>
+    <col min="7" max="8" width="9" style="1"/>
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="23">
+        <v>45842</v>
+      </c>
+      <c r="F3" s="24">
+        <v>45837</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="22"/>
+      <c r="B4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="23"/>
+      <c r="F4" s="25"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="22"/>
+      <c r="B5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="23">
+        <v>45882</v>
+      </c>
+      <c r="F5" s="24">
+        <v>45874</v>
+      </c>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="22"/>
+      <c r="B6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="23"/>
+      <c r="F6" s="25"/>
+    </row>
+    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="14">
+        <v>45874</v>
+      </c>
+      <c r="F7" s="20">
+        <v>45870</v>
+      </c>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="23">
+        <v>45848</v>
+      </c>
+      <c r="F8" s="24">
+        <v>45831</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="22"/>
+      <c r="B9" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D9" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="23"/>
+      <c r="F9" s="24"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="22"/>
+      <c r="B10" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="14">
+        <v>45909</v>
+      </c>
+      <c r="F10" s="20">
+        <v>45856</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="30" x14ac:dyDescent="0.3">
+      <c r="B14" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E14" s="14">
+        <v>45862</v>
+      </c>
+      <c r="F14" s="20">
+        <v>45842</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="20">
+        <v>45884</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B20" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="9"/>
+      <c r="D20" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B23" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F5:F6"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B9557B1-C6FF-4A2A-B830-D57FA160F354}">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.75" customWidth="1"/>
+    <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.375" customWidth="1"/>
+    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.875" customWidth="1"/>
+    <col min="7" max="7" width="9" style="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+    </row>
+    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="11"/>
       <c r="B2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="F2" s="19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="16">
-        <v>45874</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="17">
-        <v>45882</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="12"/>
-      <c r="B5" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="17"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="12"/>
-      <c r="B6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="17">
-        <v>45842</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="12"/>
-      <c r="B7" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="17"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="12"/>
-      <c r="B8" s="6" t="s">
+      <c r="B3" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="18">
+        <v>45848</v>
+      </c>
+      <c r="F3" s="20">
+        <v>45831</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="22"/>
+      <c r="B4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="18">
+        <v>45909</v>
+      </c>
+      <c r="F4" s="20">
+        <v>45856</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.3">
+      <c r="A5" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="15">
+        <v>45856</v>
+      </c>
+      <c r="F5" s="20">
+        <v>45836</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="2" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="22"/>
+      <c r="B6" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="23">
+        <v>45883</v>
+      </c>
+      <c r="F6" s="24">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="2" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="22"/>
+      <c r="B7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="23"/>
+      <c r="F7" s="25"/>
+    </row>
+    <row r="8" spans="1:7" s="2" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="22"/>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="15">
+        <v>45887</v>
+      </c>
+      <c r="F8" s="20">
+        <v>45856</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="17"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="17">
-        <v>45848</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="12"/>
-      <c r="B10" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="17"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="12"/>
-      <c r="B11" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="16">
-        <v>45909</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.3">
-      <c r="B15" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="16">
-        <v>45862</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B19" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B22" s="5" t="s">
-        <v>31</v>
-      </c>
+      <c r="B9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="18">
+        <v>45920</v>
+      </c>
+      <c r="F9" s="20">
+        <v>45877</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="G10" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="E9:E10"/>
+  <mergeCells count="5">
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="F6:F7"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="A3:A4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
